--- a/output/出雲駅伝_振り返り分析.xlsx
+++ b/output/出雲駅伝_振り返り分析.xlsx
@@ -13,19 +13,21 @@
     <sheet name="出雲区間記録" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="5000m比較" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="合宿走行距離" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="合宿消化率" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="月間走行距離" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="合宿メニュー_2023" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="合宿メニュー_2024" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="合宿メニュー_2025" sheetId="10" state="visible" r:id="rId12"/>
-    <sheet name="合宿メニュー_2026" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="合宿距離×区間順位" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="合宿消化率" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="月間走行距離" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="合宿メニュー_2023" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="合宿メニュー_2024" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="合宿メニュー_2025" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="合宿メニュー_2026" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">5000m比較!$A$4:$L$34</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">出雲区間記録!$A$4:$M$34</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">合宿消化率!$A$4:$G$28</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">合宿消化率!$A$4:$G$28</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">合宿走行距離!$A$4:$G$28</definedName>
-    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">月間走行距離!$A$4:$P$22</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'合宿距離×区間順位'!$A$4:$J$28</definedName>
+    <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">月間走行距離!$A$4:$P$22</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -435,7 +437,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="427">
   <si>
     <r>
       <rPr>
@@ -837,6 +839,114 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">年）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">合宿距離</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">×</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">区間順位</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次合宿の距離と区間順位・日本人トップとの差・悪化率を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">表に。年平均、相関係数、区間</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位以内との比較つき</t>
     </r>
   </si>
   <si>
@@ -5171,6 +5281,734 @@
   <si>
     <t xml:space="preserve">出雲
 区間</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">夏合宿の走行距離と出雲の区間順位：出雲メンバー（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2023</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">値はすべて「合宿走行距離」「</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5000m</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">比較」「出雲区間記録」シートからの参照式。区間順位は留学生を含む公式記録。日本人トップとの差は</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">区が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5km</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">あたり、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">区が</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10km</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">あたりの秒差。悪化率＝出雲</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5km</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">換算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">÷2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">週間前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5000m−1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日あたり
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(km)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+2</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次
+合計</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(km)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日本人トップ
+との差</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">秒</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年ごとの</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人平均</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">区間順位
+平均</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">区間順位との相関係数（延べ</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">24</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">指標</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次合宿の距離</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次合宿の</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日あたり距離</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次合宿の距離</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">次の合計</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">※正の値＝その指標が大きい選手ほど区間順位が悪い。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年は順位・距離ともに全体が高く、年の影響が混ざっている点に注意</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">区間</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位以内とそれ以外の比較</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">区分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">人数</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">区間</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">区間</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="HGPｺﾞｼｯｸM"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位以下</t>
+    </r>
   </si>
   <si>
     <r>
@@ -11266,6 +12104,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="170" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -11276,10 +12118,6 @@
     </xf>
     <xf numFmtId="172" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -11303,7 +12141,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="76">
+  <dxfs count="94">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -11760,6 +12598,158 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FF71C27B"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF96CC7D"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB1D47F"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC9DB80"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCBDC81"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD3DE81"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD8DF81"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDDE182"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFB9774"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFB9975"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCA878"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFCB37A"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFDC17C"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFED781"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFED981"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFEEA83"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFE684"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEA84"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFEB84"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FF8ACA7E"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
@@ -11909,14 +12899,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFEEA83"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -11998,6 +12980,10 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -12182,7 +13168,7 @@
     <tabColor rgb="FF1E5945"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -12240,7 +13226,7 @@
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="7" t="s">
         <v>12</v>
       </c>
     </row>
@@ -12256,20 +13242,20 @@
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="B12" s="7" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="5" t="s">
+      <c r="A14" s="3" t="s">
         <v>19</v>
       </c>
     </row>
@@ -12297,7 +13283,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
         <v>26</v>
       </c>
@@ -12305,7 +13291,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
         <v>28</v>
       </c>
@@ -12313,86 +13299,94 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
         <v>30</v>
       </c>
+      <c r="B20" s="5" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="7" t="s">
+      <c r="A22" s="3" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="5" t="s">
         <v>33</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>33</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>37</v>
       </c>
     </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>38</v>
+      <c r="A29" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -12412,7 +13406,7 @@
     <tabColor rgb="FF7FA99B"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -12422,494 +13416,442 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="32" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="41" t="s">
-        <v>210</v>
+      <c r="A2" s="38" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="41" t="s">
-        <v>211</v>
+      <c r="A3" s="38" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="41" t="s">
-        <v>212</v>
+      <c r="A4" s="38" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="42" t="s">
-        <v>326</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="43" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>328</v>
+        <v>245</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>329</v>
+        <v>240</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>330</v>
+        <v>241</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>331</v>
+        <v>306</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>332</v>
+        <v>307</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>220</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>239</v>
+        <v>309</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>228</v>
+        <v>311</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>228</v>
+        <v>312</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>228</v>
+        <v>313</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>238</v>
+        <v>314</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="H12" s="13" t="s">
-        <v>228</v>
+        <v>315</v>
+      </c>
+      <c r="H12" s="44" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>289</v>
+        <v>317</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>334</v>
+        <v>249</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>335</v>
+        <v>249</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>336</v>
+        <v>249</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>337</v>
+        <v>249</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>338</v>
+        <v>249</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>339</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>333</v>
+        <v>310</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>228</v>
+        <v>319</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>238</v>
+        <v>320</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>228</v>
+        <v>321</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>238</v>
+        <v>322</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>228</v>
+        <v>323</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>228</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>257</v>
+        <v>325</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>289</v>
+        <v>326</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>340</v>
+        <v>281</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="E15" s="44" t="s">
-        <v>227</v>
+        <v>281</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>281</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>343</v>
+        <v>281</v>
+      </c>
+      <c r="G15" s="44" t="s">
+        <v>327</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="E16" s="44" t="s">
-        <v>229</v>
-      </c>
-      <c r="F16" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>260</v>
+        <v>281</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="43" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="43" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="D19" s="11" t="s">
+      <c r="A18" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="H18" s="11" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="13" t="s">
         <v>329</v>
       </c>
-      <c r="E19" s="11" t="s">
+      <c r="B19" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="F19" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>220</v>
+      <c r="C19" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F19" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>348</v>
+        <v>288</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>349</v>
+        <v>331</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>350</v>
+        <v>254</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>350</v>
+        <v>254</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>350</v>
+        <v>334</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>228</v>
+        <v>287</v>
+      </c>
+      <c r="C22" s="44" t="s">
+        <v>336</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>350</v>
+        <v>300</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="13" t="s">
-        <v>348</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="E23" s="13" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="43" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="11" t="s">
         <v>238</v>
       </c>
-      <c r="F23" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="13" t="s">
-        <v>353</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="D24" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="E24" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="F24" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="43" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>329</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="G27" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="H27" s="11" t="s">
-        <v>220</v>
+      <c r="B25" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>306</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>307</v>
+      </c>
+      <c r="H25" s="11" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F26" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H26" s="44" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="13" t="s">
+        <v>297</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>271</v>
+        <v>342</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>238</v>
+        <v>300</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>317</v>
+        <v>344</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="G30" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -12939,494 +13881,1011 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="32" t="s">
-        <v>360</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="41" t="s">
-        <v>210</v>
+      <c r="A2" s="38" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="41" t="s">
-        <v>211</v>
+      <c r="A3" s="38" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="41" t="s">
-        <v>212</v>
+      <c r="A4" s="38" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="42" t="s">
-        <v>361</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="43" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="C11" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="H11" s="11" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="F12" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>355</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="F13" s="13" t="s">
+        <v>358</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>354</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="F14" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>278</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="E15" s="44" t="s">
+        <v>248</v>
+      </c>
+      <c r="F15" s="13" t="s">
         <v>363</v>
       </c>
+      <c r="G15" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>366</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="E16" s="44" t="s">
+        <v>250</v>
+      </c>
+      <c r="F16" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="43" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="H19" s="11" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="F20" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="F21" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="G21" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>369</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="F24" s="13" t="s">
+        <v>371</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="43" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>349</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>352</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>292</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="13" t="s">
+        <v>301</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="F31" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>249</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF7FA99B"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="15"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="32" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="38" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="38" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="38" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="24" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="24" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="42" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="43" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>384</v>
+      </c>
       <c r="D11" s="11" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E12" s="44" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E13" s="44" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C16" s="44" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="43" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="43" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -13462,12 +14921,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -13488,60 +14947,60 @@
     </row>
     <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L4" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="M4" s="11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" s="14" t="n">
         <v>4</v>
@@ -13602,7 +15061,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B6" s="14" t="n">
         <v>4</v>
@@ -13667,7 +15126,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B7" s="14" t="n">
         <v>3</v>
@@ -13732,7 +15191,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B8" s="14" t="n">
         <v>7</v>
@@ -13797,7 +15256,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B9" s="14" t="n">
         <v>11</v>
@@ -13862,32 +15321,32 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B12" s="11"/>
       <c r="C12" s="11"/>
       <c r="D12" s="11"/>
       <c r="E12" s="11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F13" s="21" t="n">
         <f aca="false">CORREL(E5:E9,F5:F9)</f>
@@ -13896,13 +15355,13 @@
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
       <c r="E14" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F14" s="21" t="n">
         <f aca="false">CORREL(E5:E9,B5:B9)</f>
@@ -13911,13 +15370,13 @@
     </row>
     <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="13" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F15" s="21" t="n">
         <f aca="false">CORREL(F5:F9,B5:B9)</f>
@@ -13926,13 +15385,13 @@
     </row>
     <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F16" s="21" t="n">
         <f aca="false">CORREL(I6:I9,B6:B9)</f>
@@ -13941,13 +15400,13 @@
     </row>
     <row r="17" customFormat="false" ht="26.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="13" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F17" s="21" t="n">
         <f aca="false">CORREL(I6:I9,F6:F9)</f>
@@ -13956,24 +15415,24 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14098,7 +15557,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="24" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -14176,12 +15635,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -14198,48 +15657,48 @@
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="I4" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="J4" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="J4" s="11" t="s">
-        <v>87</v>
-      </c>
       <c r="K4" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="L4" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="L4" s="11" t="s">
-        <v>88</v>
-      </c>
       <c r="M4" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
@@ -14252,10 +15711,10 @@
         <v>5</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F5" s="28" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G5" s="29" t="n">
         <v>0.0156481481481482</v>
@@ -14265,7 +15724,7 @@
         <v>0.00978009259259259</v>
       </c>
       <c r="I5" s="28" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="J5" s="29" t="n">
         <v>0.0157986111111111</v>
@@ -14284,7 +15743,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B6" s="28" t="n">
         <v>2</v>
@@ -14297,10 +15756,10 @@
         <v>5</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F6" s="28" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G6" s="29" t="n">
         <v>0.0107291666666667</v>
@@ -14310,7 +15769,7 @@
         <v>0.00924928160919541</v>
       </c>
       <c r="I6" s="28" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="J6" s="29" t="n">
         <v>0.0109027777777778</v>
@@ -14329,7 +15788,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B7" s="28" t="n">
         <v>3</v>
@@ -14342,10 +15801,10 @@
         <v>5</v>
       </c>
       <c r="E7" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="F7" s="28" t="s">
         <v>98</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>96</v>
       </c>
       <c r="G7" s="29" t="n">
         <v>0.0165509259259259</v>
@@ -14355,7 +15814,7 @@
         <v>0.00973583877995643</v>
       </c>
       <c r="I7" s="28" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J7" s="29" t="n">
         <v>0.0165625</v>
@@ -14374,7 +15833,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B8" s="28" t="n">
         <v>4</v>
@@ -14387,10 +15846,10 @@
         <v>5</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F8" s="28" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G8" s="29" t="n">
         <v>0.0123842592592593</v>
@@ -14400,7 +15859,7 @@
         <v>0.00998730585424134</v>
       </c>
       <c r="I8" s="28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="J8" s="29" t="n">
         <v>0.0130208333333333</v>
@@ -14419,7 +15878,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B9" s="28" t="n">
         <v>5</v>
@@ -14432,10 +15891,10 @@
         <v>5</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F9" s="28" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G9" s="29" t="n">
         <v>0.0132407407407407</v>
@@ -14445,7 +15904,7 @@
         <v>0.0103443287037037</v>
       </c>
       <c r="I9" s="28" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="J9" s="29" t="n">
         <v>0.0135416666666667</v>
@@ -14464,7 +15923,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B10" s="28" t="n">
         <v>6</v>
@@ -14477,10 +15936,10 @@
         <v>10</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G10" s="29" t="n">
         <v>0.0203819444444445</v>
@@ -14490,7 +15949,7 @@
         <v>0.0199822984749455</v>
       </c>
       <c r="I10" s="28" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J10" s="29" t="n">
         <v>0.0206597222222222</v>
@@ -14509,7 +15968,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>1</v>
@@ -14522,10 +15981,10 @@
         <v>5</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G11" s="31" t="n">
         <v>0.0157986111111111</v>
@@ -14535,7 +15994,7 @@
         <v>0.00987413194444444</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J11" s="31" t="n">
         <v>0.01625</v>
@@ -14554,7 +16013,7 @@
     </row>
     <row r="12" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>2</v>
@@ -14567,10 +16026,10 @@
         <v>5</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G12" s="31" t="n">
         <v>0.0112037037037037</v>
@@ -14580,7 +16039,7 @@
         <v>0.00965836526181354</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J12" s="31" t="n">
         <v>0.0112037037037037</v>
@@ -14599,7 +16058,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>3</v>
@@ -14612,10 +16071,10 @@
         <v>5</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G13" s="31" t="n">
         <v>0.0168981481481482</v>
@@ -14625,7 +16084,7 @@
         <v>0.0099400871459695</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J13" s="31" t="n">
         <v>0.0172685185185185</v>
@@ -14644,7 +16103,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>4</v>
@@ -14657,10 +16116,10 @@
         <v>5</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G14" s="31" t="n">
         <v>0.0122106481481482</v>
@@ -14670,7 +16129,7 @@
         <v>0.00984729689366786</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J14" s="31" t="n">
         <v>0.0122106481481482</v>
@@ -14689,7 +16148,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>5</v>
@@ -14702,10 +16161,10 @@
         <v>5</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G15" s="31" t="n">
         <v>0.0123958333333333</v>
@@ -14715,7 +16174,7 @@
         <v>0.00968424479166666</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J15" s="31" t="n">
         <v>0.0132523148148148</v>
@@ -14734,7 +16193,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>6</v>
@@ -14747,10 +16206,10 @@
         <v>10</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G16" s="31" t="n">
         <v>0.0201388888888889</v>
@@ -14760,7 +16219,7 @@
         <v>0.019744008714597</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J16" s="31" t="n">
         <v>0.0211111111111111</v>
@@ -14779,7 +16238,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B17" s="28" t="n">
         <v>1</v>
@@ -14792,10 +16251,10 @@
         <v>5</v>
       </c>
       <c r="E17" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" s="28" t="s">
         <v>117</v>
-      </c>
-      <c r="F17" s="28" t="s">
-        <v>115</v>
       </c>
       <c r="G17" s="29" t="n">
         <v>0.0164351851851852</v>
@@ -14805,7 +16264,7 @@
         <v>0.0102719907407407</v>
       </c>
       <c r="I17" s="28" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J17" s="29" t="n">
         <v>0.0164351851851852</v>
@@ -14824,7 +16283,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B18" s="28" t="n">
         <v>2</v>
@@ -14837,10 +16296,10 @@
         <v>5</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G18" s="29" t="n">
         <v>0.0109490740740741</v>
@@ -14850,7 +16309,7 @@
         <v>0.00943885696040868</v>
       </c>
       <c r="I18" s="28" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J18" s="29" t="n">
         <v>0.0114814814814815</v>
@@ -14869,7 +16328,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B19" s="28" t="n">
         <v>3</v>
@@ -14882,10 +16341,10 @@
         <v>5</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F19" s="28" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G19" s="29" t="n">
         <v>0.0165740740740741</v>
@@ -14895,7 +16354,7 @@
         <v>0.00974945533769063</v>
       </c>
       <c r="I19" s="28" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J19" s="29" t="n">
         <v>0.0166087962962963</v>
@@ -14914,7 +16373,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B20" s="28" t="n">
         <v>4</v>
@@ -14927,10 +16386,10 @@
         <v>5</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F20" s="28" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G20" s="29" t="n">
         <v>0.0122916666666667</v>
@@ -14940,7 +16399,7 @@
         <v>0.00991263440860215</v>
       </c>
       <c r="I20" s="28" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="J20" s="29" t="n">
         <v>0.0124768518518519</v>
@@ -14959,7 +16418,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B21" s="28" t="n">
         <v>5</v>
@@ -14972,10 +16431,10 @@
         <v>5</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F21" s="28" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G21" s="29" t="n">
         <v>0.0126388888888889</v>
@@ -14985,7 +16444,7 @@
         <v>0.00987413194444445</v>
       </c>
       <c r="I21" s="28" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="J21" s="29" t="n">
         <v>0.012962962962963</v>
@@ -15004,7 +16463,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B22" s="28" t="n">
         <v>6</v>
@@ -15017,10 +16476,10 @@
         <v>10</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G22" s="29" t="n">
         <v>0.0201736111111111</v>
@@ -15030,7 +16489,7 @@
         <v>0.0197780501089325</v>
       </c>
       <c r="I22" s="28" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J22" s="29" t="n">
         <v>0.0205902777777778</v>
@@ -15049,7 +16508,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>1</v>
@@ -15062,10 +16521,10 @@
         <v>5</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G23" s="31" t="n">
         <v>0.0162962962962963</v>
@@ -15075,7 +16534,7 @@
         <v>0.0101851851851852</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J23" s="31" t="n">
         <v>0.0165046296296296</v>
@@ -15094,7 +16553,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>2</v>
@@ -15107,10 +16566,10 @@
         <v>5</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G24" s="31" t="n">
         <v>0.0110763888888889</v>
@@ -15120,7 +16579,7 @@
         <v>0.00954861111111111</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J24" s="31" t="n">
         <v>0.0117592592592593</v>
@@ -15139,7 +16598,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B25" s="8" t="n">
         <v>3</v>
@@ -15152,10 +16611,10 @@
         <v>5</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G25" s="31" t="n">
         <v>0.0165393518518519</v>
@@ -15165,7 +16624,7 @@
         <v>0.00972903050108932</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J25" s="31" t="n">
         <v>0.0175578703703704</v>
@@ -15184,7 +16643,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>4</v>
@@ -15197,10 +16656,10 @@
         <v>5</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G26" s="31" t="n">
         <v>0.012037037037037</v>
@@ -15210,7 +16669,7 @@
         <v>0.00970728793309439</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J26" s="31" t="n">
         <v>0.0123148148148148</v>
@@ -15229,7 +16688,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B27" s="8" t="n">
         <v>5</v>
@@ -15242,10 +16701,10 @@
         <v>5</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G27" s="31" t="n">
         <v>0.0124305555555556</v>
@@ -15255,7 +16714,7 @@
         <v>0.00971137152777778</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J27" s="31" t="n">
         <v>0.0124305555555556</v>
@@ -15274,7 +16733,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B28" s="8" t="n">
         <v>6</v>
@@ -15287,10 +16746,10 @@
         <v>10</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G28" s="31" t="n">
         <v>0.0203125</v>
@@ -15300,7 +16759,7 @@
         <v>0.0199142156862745</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J28" s="31" t="n">
         <v>0.0203125</v>
@@ -15319,7 +16778,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B29" s="28" t="n">
         <v>1</v>
@@ -15332,10 +16791,10 @@
         <v>5</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F29" s="28" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G29" s="29" t="n">
         <v>0.0157638888888889</v>
@@ -15345,7 +16804,7 @@
         <v>0.00985243055555556</v>
       </c>
       <c r="I29" s="28" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J29" s="29" t="n">
         <v>0.0158333333333333</v>
@@ -15364,7 +16823,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B30" s="28" t="n">
         <v>2</v>
@@ -15377,10 +16836,10 @@
         <v>5</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F30" s="28" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G30" s="29" t="n">
         <v>0.0109027777777778</v>
@@ -15390,7 +16849,7 @@
         <v>0.00939894636015326</v>
       </c>
       <c r="I30" s="28" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="J30" s="29" t="n">
         <v>0.0112268518518519</v>
@@ -15409,7 +16868,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B31" s="28" t="n">
         <v>3</v>
@@ -15422,10 +16881,10 @@
         <v>5</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F31" s="28" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="G31" s="29" t="n">
         <v>0.0163078703703704</v>
@@ -15435,7 +16894,7 @@
         <v>0.00959286492374728</v>
       </c>
       <c r="I31" s="28" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J31" s="29" t="n">
         <v>0.0171180555555556</v>
@@ -15454,7 +16913,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B32" s="28" t="n">
         <v>4</v>
@@ -15467,10 +16926,10 @@
         <v>5</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F32" s="28" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G32" s="29" t="n">
         <v>0.0119212962962963</v>
@@ -15480,7 +16939,7 @@
         <v>0.0096139486260454</v>
       </c>
       <c r="I32" s="28" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="J32" s="29" t="n">
         <v>0.0124884259259259</v>
@@ -15499,7 +16958,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B33" s="28" t="n">
         <v>5</v>
@@ -15512,10 +16971,10 @@
         <v>5</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F33" s="28" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G33" s="29" t="n">
         <v>0.0122106481481482</v>
@@ -15525,7 +16984,7 @@
         <v>0.00953956886574074</v>
       </c>
       <c r="I33" s="28" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J33" s="29" t="n">
         <v>0.0124074074074074</v>
@@ -15544,7 +17003,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B34" s="28" t="n">
         <v>6</v>
@@ -15557,10 +17016,10 @@
         <v>10</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F34" s="28" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G34" s="29" t="n">
         <v>0.0201388888888889</v>
@@ -15570,7 +17029,7 @@
         <v>0.019744008714597</v>
       </c>
       <c r="I34" s="28" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J34" s="29" t="n">
         <v>0.0211226851851852</v>
@@ -15641,12 +17100,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="32" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -15662,57 +17121,57 @@
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J4" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" s="28" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D5" s="33" t="n">
         <v>0.00959375</v>
       </c>
       <c r="E5" s="28" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F5" s="29" t="n">
         <v>0.0157986111111111</v>
@@ -15741,19 +17200,19 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B6" s="28" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="28" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D6" s="33" t="n">
         <v>0.00956956018518518</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F6" s="29" t="n">
         <v>0.0109027777777778</v>
@@ -15782,19 +17241,19 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B7" s="28" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D7" s="33" t="n">
         <v>0.00952627314814815</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F7" s="29" t="n">
         <v>0.0165625</v>
@@ -15823,19 +17282,19 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B8" s="28" t="n">
         <v>4</v>
       </c>
       <c r="C8" s="28" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D8" s="33" t="n">
         <v>0.00991412037037037</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F8" s="29" t="n">
         <v>0.0130208333333333</v>
@@ -15864,19 +17323,19 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B9" s="28" t="n">
         <v>5</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D9" s="33" t="n">
         <v>0.00985868055555556</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F9" s="29" t="n">
         <v>0.0135416666666667</v>
@@ -15905,19 +17364,19 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B10" s="28" t="n">
         <v>6</v>
       </c>
       <c r="C10" s="28" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D10" s="33" t="n">
         <v>0.00955810185185185</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F10" s="29" t="n">
         <v>0.0206597222222222</v>
@@ -15946,19 +17405,19 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D11" s="36" t="n">
         <v>0.00945520833333333</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F11" s="31" t="n">
         <v>0.01625</v>
@@ -15987,19 +17446,19 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D12" s="36" t="n">
         <v>0.00945081018518519</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F12" s="31" t="n">
         <v>0.0112037037037037</v>
@@ -16028,19 +17487,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>3</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D13" s="36" t="n">
         <v>0.0094494212962963</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F13" s="31" t="n">
         <v>0.0172685185185185</v>
@@ -16069,19 +17528,19 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D14" s="36" t="n">
         <v>0.00943333333333333</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F14" s="31" t="n">
         <v>0.0122106481481482</v>
@@ -16110,19 +17569,19 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>5</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D15" s="36" t="n">
         <v>0.00945289351851852</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F15" s="31" t="n">
         <v>0.0132523148148148</v>
@@ -16151,19 +17610,19 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>6</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D16" s="36" t="n">
         <v>0.00962106481481482</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F16" s="31" t="n">
         <v>0.0211111111111111</v>
@@ -16192,19 +17651,19 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B17" s="28" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D17" s="33" t="n">
         <v>0.0096212962962963</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F17" s="29" t="n">
         <v>0.0164351851851852</v>
@@ -16233,19 +17692,19 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B18" s="28" t="n">
         <v>2</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D18" s="33" t="n">
         <v>0.0095974537037037</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F18" s="29" t="n">
         <v>0.0114814814814815</v>
@@ -16274,19 +17733,19 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B19" s="28" t="n">
         <v>3</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D19" s="33" t="n">
         <v>0.00949016203703704</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F19" s="29" t="n">
         <v>0.0166087962962963</v>
@@ -16315,19 +17774,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B20" s="28" t="n">
         <v>4</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D20" s="33" t="n">
         <v>0.00946493055555556</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F20" s="29" t="n">
         <v>0.0124768518518519</v>
@@ -16356,19 +17815,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B21" s="28" t="n">
         <v>5</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D21" s="33" t="n">
         <v>0.0096494212962963</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F21" s="29" t="n">
         <v>0.012962962962963</v>
@@ -16397,19 +17856,19 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B22" s="28" t="n">
         <v>6</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D22" s="33" t="n">
         <v>0.00973819444444445</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F22" s="29" t="n">
         <v>0.0205902777777778</v>
@@ -16438,19 +17897,19 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D23" s="36" t="n">
         <v>0.00951111111111111</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F23" s="31" t="n">
         <v>0.0165046296296296</v>
@@ -16479,19 +17938,19 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>2</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D24" s="36" t="n">
         <v>0.00970798611111111</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F24" s="31" t="n">
         <v>0.0117592592592593</v>
@@ -16520,19 +17979,19 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B25" s="8" t="n">
         <v>3</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D25" s="36" t="n">
         <v>0.00958854166666667</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F25" s="31" t="n">
         <v>0.0175578703703704</v>
@@ -16561,19 +18020,19 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>4</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D26" s="36" t="n">
         <v>0.0095369212962963</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F26" s="31" t="n">
         <v>0.0123148148148148</v>
@@ -16602,19 +18061,19 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B27" s="8" t="n">
         <v>5</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D27" s="36" t="n">
         <v>0.00960138888888889</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F27" s="31" t="n">
         <v>0.0124305555555556</v>
@@ -16643,19 +18102,19 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B28" s="8" t="n">
         <v>6</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D28" s="36" t="n">
         <v>0.00942141203703704</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="F28" s="31" t="n">
         <v>0.0203125</v>
@@ -16684,19 +18143,19 @@
     </row>
     <row r="29" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B29" s="28" t="n">
         <v>1</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D29" s="29" t="n">
         <v>0.00945601851851852</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F29" s="29" t="n">
         <v>0.0158333333333333</v>
@@ -16725,19 +18184,19 @@
     </row>
     <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B30" s="28" t="n">
         <v>2</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D30" s="29" t="n">
         <v>0.00944444444444445</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F30" s="29" t="n">
         <v>0.0112268518518519</v>
@@ -16766,19 +18225,19 @@
     </row>
     <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B31" s="28" t="n">
         <v>3</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D31" s="29" t="n">
         <v>0.00943287037037037</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F31" s="29" t="n">
         <v>0.0171180555555556</v>
@@ -16807,19 +18266,19 @@
     </row>
     <row r="32" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B32" s="28" t="n">
         <v>4</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D32" s="29" t="n">
         <v>0.00951388888888889</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F32" s="29" t="n">
         <v>0.0124884259259259</v>
@@ -16848,19 +18307,19 @@
     </row>
     <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B33" s="28" t="n">
         <v>5</v>
       </c>
       <c r="C33" s="28" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D33" s="29" t="n">
         <v>0.00949074074074074</v>
       </c>
       <c r="E33" s="28" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F33" s="29" t="n">
         <v>0.0124074074074074</v>
@@ -16889,19 +18348,19 @@
     </row>
     <row r="34" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="25" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B34" s="28" t="n">
         <v>6</v>
       </c>
       <c r="C34" s="28" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D34" s="29" t="n">
         <v>0.00947916666666667</v>
       </c>
       <c r="E34" s="28" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F34" s="29" t="n">
         <v>0.0211226851851852</v>
@@ -16975,12 +18434,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -16991,33 +18450,33 @@
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C5" s="26" t="n">
         <v>559</v>
@@ -17039,10 +18498,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C6" s="26" t="n">
         <v>509.5</v>
@@ -17064,10 +18523,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C7" s="26" t="n">
         <v>647</v>
@@ -17089,10 +18548,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C8" s="26" t="n">
         <v>569</v>
@@ -17114,10 +18573,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C9" s="26" t="n">
         <v>708</v>
@@ -17139,10 +18598,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C10" s="26" t="n">
         <v>459</v>
@@ -17164,10 +18623,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C11" s="18" t="n">
         <v>409</v>
@@ -17189,10 +18648,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C12" s="18" t="n">
         <v>485</v>
@@ -17214,10 +18673,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C13" s="18" t="n">
         <v>453</v>
@@ -17239,10 +18698,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C14" s="18" t="n">
         <v>500</v>
@@ -17264,10 +18723,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C15" s="18" t="n">
         <v>536</v>
@@ -17289,10 +18748,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C16" s="18" t="n">
         <v>463</v>
@@ -17314,10 +18773,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C17" s="26" t="n">
         <v>612</v>
@@ -17339,10 +18798,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C18" s="26" t="n">
         <v>556</v>
@@ -17364,10 +18823,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C19" s="26" t="n">
         <v>496</v>
@@ -17389,10 +18848,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C20" s="26" t="n">
         <v>591</v>
@@ -17414,10 +18873,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C21" s="26" t="n">
         <v>721</v>
@@ -17439,10 +18898,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C22" s="26" t="n">
         <v>496</v>
@@ -17464,10 +18923,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C23" s="18" t="n">
         <v>502</v>
@@ -17489,10 +18948,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C24" s="18" t="n">
         <v>595</v>
@@ -17514,10 +18973,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C25" s="18" t="n">
         <v>500</v>
@@ -17539,10 +18998,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C26" s="18" t="n">
         <v>616</v>
@@ -17564,10 +19023,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C27" s="18" t="n">
         <v>501</v>
@@ -17589,10 +19048,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C28" s="18" t="n">
         <v>619</v>
@@ -17634,6 +19093,1398 @@
     <tabColor rgb="FF7FA99B"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
+  <dimension ref="A1:J49"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="5" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+    </row>
+    <row r="4" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="D5" s="27" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A5,5000m比較!$C$5:$C$34,$C5)</f>
+        <v>6</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A5,合宿走行距離!$B$5:$B$28,$C5)</f>
+        <v>559</v>
+      </c>
+      <c r="F5" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A5,合宿走行距離!$B$5:$B$28,$C5)</f>
+        <v>25.4090909090909</v>
+      </c>
+      <c r="G5" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A5,合宿走行距離!$B$5:$B$28,$C5)</f>
+        <v>272</v>
+      </c>
+      <c r="H5" s="26" t="n">
+        <f aca="false">E5+G5</f>
+        <v>831</v>
+      </c>
+      <c r="I5" s="30" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A5,出雲区間記録!$B$5:$B$34,$B5)</f>
+        <v>24.4</v>
+      </c>
+      <c r="J5" s="35" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A5,5000m比較!$C$5:$C$34,$C5)</f>
+        <v>0.0741434394623775</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="D6" s="27" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A6,5000m比較!$C$5:$C$34,$C6)</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A6,合宿走行距離!$B$5:$B$28,$C6)</f>
+        <v>509.5</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A6,合宿走行距離!$B$5:$B$28,$C6)</f>
+        <v>23.1590909090909</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A6,合宿走行距離!$B$5:$B$28,$C6)</f>
+        <v>234</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <f aca="false">E6+G6</f>
+        <v>743.5</v>
+      </c>
+      <c r="I6" s="30" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A6,出雲区間記録!$B$5:$B$34,$B6)</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="35" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A6,5000m比較!$C$5:$C$34,$C6)</f>
+        <v>0.0219616173176038</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="D7" s="27" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A7,5000m比較!$C$5:$C$34,$C7)</f>
+        <v>3</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A7,合宿走行距離!$B$5:$B$28,$C7)</f>
+        <v>647</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A7,合宿走行距離!$B$5:$B$28,$C7)</f>
+        <v>29.4090909090909</v>
+      </c>
+      <c r="G7" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A7,合宿走行距離!$B$5:$B$28,$C7)</f>
+        <v>160</v>
+      </c>
+      <c r="H7" s="26" t="n">
+        <f aca="false">E7+G7</f>
+        <v>807</v>
+      </c>
+      <c r="I7" s="30" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A7,出雲区間記録!$B$5:$B$34,$B7)</f>
+        <v>18.8</v>
+      </c>
+      <c r="J7" s="35" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A7,5000m比較!$C$5:$C$34,$C7)</f>
+        <v>0.0749813931672396</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="D8" s="27" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A8,5000m比較!$C$5:$C$34,$C8)</f>
+        <v>1</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A8,合宿走行距離!$B$5:$B$28,$C8)</f>
+        <v>569</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A8,合宿走行距離!$B$5:$B$28,$C8)</f>
+        <v>25.8636363636364</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A8,合宿走行距離!$B$5:$B$28,$C8)</f>
+        <v>237</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <f aca="false">E8+G8</f>
+        <v>806</v>
+      </c>
+      <c r="I8" s="30" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A8,出雲区間記録!$B$5:$B$34,$B8)</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="35" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A8,5000m比較!$C$5:$C$34,$C8)</f>
+        <v>0.0438830629329889</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="D9" s="27" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A9,5000m比較!$C$5:$C$34,$C9)</f>
+        <v>9</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A9,合宿走行距離!$B$5:$B$28,$C9)</f>
+        <v>708</v>
+      </c>
+      <c r="F9" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A9,合宿走行距離!$B$5:$B$28,$C9)</f>
+        <v>32.1818181818182</v>
+      </c>
+      <c r="G9" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A9,合宿走行距離!$B$5:$B$28,$C9)</f>
+        <v>271</v>
+      </c>
+      <c r="H9" s="26" t="n">
+        <f aca="false">E9+G9</f>
+        <v>979</v>
+      </c>
+      <c r="I9" s="30" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A9,出雲区間記録!$B$5:$B$34,$B9)</f>
+        <v>57.8</v>
+      </c>
+      <c r="J9" s="35" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A9,5000m比較!$C$5:$C$34,$C9)</f>
+        <v>0.0952594492671992</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B10" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="D10" s="27" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A10,5000m比較!$C$5:$C$34,$C10)</f>
+        <v>7</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A10,合宿走行距離!$B$5:$B$28,$C10)</f>
+        <v>459</v>
+      </c>
+      <c r="F10" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A10,合宿走行距離!$B$5:$B$28,$C10)</f>
+        <v>20.8636363636364</v>
+      </c>
+      <c r="G10" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A10,合宿走行距離!$B$5:$B$28,$C10)</f>
+        <v>220</v>
+      </c>
+      <c r="H10" s="26" t="n">
+        <f aca="false">E10+G10</f>
+        <v>679</v>
+      </c>
+      <c r="I10" s="30" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A10,出雲区間記録!$B$5:$B$34,$B10)</f>
+        <v>82.4</v>
+      </c>
+      <c r="J10" s="35" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A10,5000m比較!$C$5:$C$34,$C10)</f>
+        <v>0.0756173123436992</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A11,5000m比較!$C$5:$C$34,$C11)</f>
+        <v>1</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A11,合宿走行距離!$B$5:$B$28,$C11)</f>
+        <v>409</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A11,合宿走行距離!$B$5:$B$28,$C11)</f>
+        <v>21.5263157894737</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A11,合宿走行距離!$B$5:$B$28,$C11)</f>
+        <v>202</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <f aca="false">E11+G11</f>
+        <v>611</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A11,出雲区間記録!$B$5:$B$34,$B11)</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="37" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A11,5000m比較!$C$5:$C$34,$C11)</f>
+        <v>0.0676306419016453</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="D12" s="14" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A12,5000m比較!$C$5:$C$34,$C12)</f>
+        <v>6</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A12,合宿走行距離!$B$5:$B$28,$C12)</f>
+        <v>485</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A12,合宿走行距離!$B$5:$B$28,$C12)</f>
+        <v>25.5263157894737</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A12,合宿走行距離!$B$5:$B$28,$C12)</f>
+        <v>202</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <f aca="false">E12+G12</f>
+        <v>687</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A12,出雲区間記録!$B$5:$B$34,$B12)</f>
+        <v>39.7</v>
+      </c>
+      <c r="J12" s="37" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A12,5000m比較!$C$5:$C$34,$C12)</f>
+        <v>0.0312973804214844</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A13,5000m比較!$C$5:$C$34,$C13)</f>
+        <v>3</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A13,合宿走行距離!$B$5:$B$28,$C13)</f>
+        <v>453</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A13,合宿走行距離!$B$5:$B$28,$C13)</f>
+        <v>23.8421052631579</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A13,合宿走行距離!$B$5:$B$28,$C13)</f>
+        <v>206</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <f aca="false">E13+G13</f>
+        <v>659</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A13,出雲区間記録!$B$5:$B$34,$B13)</f>
+        <v>1.8</v>
+      </c>
+      <c r="J13" s="37" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A13,5000m比較!$C$5:$C$34,$C13)</f>
+        <v>0.0294745375435375</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="D14" s="14" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A14,5000m比較!$C$5:$C$34,$C14)</f>
+        <v>5</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A14,合宿走行距離!$B$5:$B$28,$C14)</f>
+        <v>500</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A14,合宿走行距離!$B$5:$B$28,$C14)</f>
+        <v>26.3157894736842</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A14,合宿走行距離!$B$5:$B$28,$C14)</f>
+        <v>199</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <f aca="false">E14+G14</f>
+        <v>699</v>
+      </c>
+      <c r="I14" s="15" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A14,出雲区間記録!$B$5:$B$34,$B14)</f>
+        <v>12.9</v>
+      </c>
+      <c r="J14" s="37" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A14,5000m比較!$C$5:$C$34,$C14)</f>
+        <v>0.06307988641021</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="D15" s="14" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A15,5000m比較!$C$5:$C$34,$C15)</f>
+        <v>5</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A15,合宿走行距離!$B$5:$B$28,$C15)</f>
+        <v>536</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A15,合宿走行距離!$B$5:$B$28,$C15)</f>
+        <v>28.2105263157895</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A15,合宿走行距離!$B$5:$B$28,$C15)</f>
+        <v>252</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <f aca="false">E15+G15</f>
+        <v>788</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A15,出雲区間記録!$B$5:$B$34,$B15)</f>
+        <v>21.9</v>
+      </c>
+      <c r="J15" s="37" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A15,5000m比較!$C$5:$C$34,$C15)</f>
+        <v>0.0495256144222807</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="D16" s="14" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A16,5000m比較!$C$5:$C$34,$C16)</f>
+        <v>3</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A16,合宿走行距離!$B$5:$B$28,$C16)</f>
+        <v>463</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A16,合宿走行距離!$B$5:$B$28,$C16)</f>
+        <v>24.3684210526316</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A16,合宿走行距離!$B$5:$B$28,$C16)</f>
+        <v>201</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <f aca="false">E16+G16</f>
+        <v>664</v>
+      </c>
+      <c r="I16" s="15" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A16,出雲区間記録!$B$5:$B$34,$B16)</f>
+        <v>35.3</v>
+      </c>
+      <c r="J16" s="37" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A16,5000m比較!$C$5:$C$34,$C16)</f>
+        <v>0.0364625062747057</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B17" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="D17" s="27" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A17,5000m比較!$C$5:$C$34,$C17)</f>
+        <v>6</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A17,合宿走行距離!$B$5:$B$28,$C17)</f>
+        <v>612</v>
+      </c>
+      <c r="F17" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A17,合宿走行距離!$B$5:$B$28,$C17)</f>
+        <v>32.2105263157895</v>
+      </c>
+      <c r="G17" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A17,合宿走行距離!$B$5:$B$28,$C17)</f>
+        <v>212</v>
+      </c>
+      <c r="H17" s="26" t="n">
+        <f aca="false">E17+G17</f>
+        <v>824</v>
+      </c>
+      <c r="I17" s="30" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A17,出雲区間記録!$B$5:$B$34,$B17)</f>
+        <v>11.3</v>
+      </c>
+      <c r="J17" s="35" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A17,5000m比較!$C$5:$C$34,$C17)</f>
+        <v>0.0845624026479752</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="D18" s="27" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A18,5000m比較!$C$5:$C$34,$C18)</f>
+        <v>10</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A18,合宿走行距離!$B$5:$B$28,$C18)</f>
+        <v>556</v>
+      </c>
+      <c r="F18" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A18,合宿走行距離!$B$5:$B$28,$C18)</f>
+        <v>29.2631578947368</v>
+      </c>
+      <c r="G18" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A18,合宿走行距離!$B$5:$B$28,$C18)</f>
+        <v>219</v>
+      </c>
+      <c r="H18" s="26" t="n">
+        <f aca="false">E18+G18</f>
+        <v>775</v>
+      </c>
+      <c r="I18" s="30" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A18,出雲区間記録!$B$5:$B$34,$B18)</f>
+        <v>50.9</v>
+      </c>
+      <c r="J18" s="35" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A18,5000m比較!$C$5:$C$34,$C18)</f>
+        <v>0.0442219785704272</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B19" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="D19" s="27" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A19,5000m比較!$C$5:$C$34,$C19)</f>
+        <v>10</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A19,合宿走行距離!$B$5:$B$28,$C19)</f>
+        <v>496</v>
+      </c>
+      <c r="F19" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A19,合宿走行距離!$B$5:$B$28,$C19)</f>
+        <v>26.1052631578947</v>
+      </c>
+      <c r="G19" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A19,合宿走行距離!$B$5:$B$28,$C19)</f>
+        <v>222</v>
+      </c>
+      <c r="H19" s="26" t="n">
+        <f aca="false">E19+G19</f>
+        <v>718</v>
+      </c>
+      <c r="I19" s="30" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A19,出雲区間記録!$B$5:$B$34,$B19)</f>
+        <v>51.8</v>
+      </c>
+      <c r="J19" s="35" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A19,5000m比較!$C$5:$C$34,$C19)</f>
+        <v>0.077135543697834</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B20" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="D20" s="27" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A20,5000m比較!$C$5:$C$34,$C20)</f>
+        <v>8</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A20,合宿走行距離!$B$5:$B$28,$C20)</f>
+        <v>591</v>
+      </c>
+      <c r="F20" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A20,合宿走行距離!$B$5:$B$28,$C20)</f>
+        <v>31.1052631578947</v>
+      </c>
+      <c r="G20" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A20,合宿走行距離!$B$5:$B$28,$C20)</f>
+        <v>240</v>
+      </c>
+      <c r="H20" s="26" t="n">
+        <f aca="false">E20+G20</f>
+        <v>831</v>
+      </c>
+      <c r="I20" s="30" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A20,出雲区間記録!$B$5:$B$34,$B20)</f>
+        <v>19.4</v>
+      </c>
+      <c r="J20" s="35" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A20,5000m比較!$C$5:$C$34,$C20)</f>
+        <v>0.0413530699754023</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="C21" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="D21" s="27" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A21,5000m比較!$C$5:$C$34,$C21)</f>
+        <v>1</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A21,合宿走行距離!$B$5:$B$28,$C21)</f>
+        <v>721</v>
+      </c>
+      <c r="F21" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A21,合宿走行距離!$B$5:$B$28,$C21)</f>
+        <v>37.9473684210526</v>
+      </c>
+      <c r="G21" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A21,合宿走行距離!$B$5:$B$28,$C21)</f>
+        <v>266</v>
+      </c>
+      <c r="H21" s="26" t="n">
+        <f aca="false">E21+G21</f>
+        <v>987</v>
+      </c>
+      <c r="I21" s="30" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A21,出雲区間記録!$B$5:$B$34,$B21)</f>
+        <v>0</v>
+      </c>
+      <c r="J21" s="35" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A21,5000m比較!$C$5:$C$34,$C21)</f>
+        <v>0.0114548676406772</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B22" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="D22" s="27" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A22,5000m比較!$C$5:$C$34,$C22)</f>
+        <v>1</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A22,合宿走行距離!$B$5:$B$28,$C22)</f>
+        <v>496</v>
+      </c>
+      <c r="F22" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A22,合宿走行距離!$B$5:$B$28,$C22)</f>
+        <v>26.1052631578947</v>
+      </c>
+      <c r="G22" s="26" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A22,合宿走行距離!$B$5:$B$28,$C22)</f>
+        <v>224</v>
+      </c>
+      <c r="H22" s="26" t="n">
+        <f aca="false">E22+G22</f>
+        <v>720</v>
+      </c>
+      <c r="I22" s="30" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A22,出雲区間記録!$B$5:$B$34,$B22)</f>
+        <v>0</v>
+      </c>
+      <c r="J22" s="35" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A22,5000m比較!$C$5:$C$34,$C22)</f>
+        <v>0.0568593968711182</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="D23" s="14" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A23,5000m比較!$C$5:$C$34,$C23)</f>
+        <v>2</v>
+      </c>
+      <c r="E23" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A23,合宿走行距離!$B$5:$B$28,$C23)</f>
+        <v>502</v>
+      </c>
+      <c r="F23" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A23,合宿走行距離!$B$5:$B$28,$C23)</f>
+        <v>27.8888888888889</v>
+      </c>
+      <c r="G23" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A23,合宿走行距離!$B$5:$B$28,$C23)</f>
+        <v>221</v>
+      </c>
+      <c r="H23" s="18" t="n">
+        <f aca="false">E23+G23</f>
+        <v>723</v>
+      </c>
+      <c r="I23" s="15" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A23,出雲区間記録!$B$5:$B$34,$B23)</f>
+        <v>3.7</v>
+      </c>
+      <c r="J23" s="37" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A23,5000m比較!$C$5:$C$34,$C23)</f>
+        <v>0.0465116279069768</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B24" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="D24" s="14" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A24,5000m比較!$C$5:$C$34,$C24)</f>
+        <v>9</v>
+      </c>
+      <c r="E24" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A24,合宿走行距離!$B$5:$B$28,$C24)</f>
+        <v>595</v>
+      </c>
+      <c r="F24" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A24,合宿走行距離!$B$5:$B$28,$C24)</f>
+        <v>33.0555555555556</v>
+      </c>
+      <c r="G24" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A24,合宿走行距離!$B$5:$B$28,$C24)</f>
+        <v>233</v>
+      </c>
+      <c r="H24" s="18" t="n">
+        <f aca="false">E24+G24</f>
+        <v>828</v>
+      </c>
+      <c r="I24" s="15" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A24,出雲区間記録!$B$5:$B$34,$B24)</f>
+        <v>24.1</v>
+      </c>
+      <c r="J24" s="37" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A24,5000m比較!$C$5:$C$34,$C24)</f>
+        <v>0.0247633536173089</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="D25" s="14" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A25,5000m比較!$C$5:$C$34,$C25)</f>
+        <v>11</v>
+      </c>
+      <c r="E25" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A25,合宿走行距離!$B$5:$B$28,$C25)</f>
+        <v>500</v>
+      </c>
+      <c r="F25" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A25,合宿走行距離!$B$5:$B$28,$C25)</f>
+        <v>27.7777777777778</v>
+      </c>
+      <c r="G25" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A25,合宿走行距離!$B$5:$B$28,$C25)</f>
+        <v>212</v>
+      </c>
+      <c r="H25" s="18" t="n">
+        <f aca="false">E25+G25</f>
+        <v>712</v>
+      </c>
+      <c r="I25" s="15" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A25,出雲区間記録!$B$5:$B$34,$B25)</f>
+        <v>41.2</v>
+      </c>
+      <c r="J25" s="37" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A25,5000m比較!$C$5:$C$34,$C25)</f>
+        <v>0.0674846625766874</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="D26" s="14" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A26,5000m比較!$C$5:$C$34,$C26)</f>
+        <v>11</v>
+      </c>
+      <c r="E26" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A26,合宿走行距離!$B$5:$B$28,$C26)</f>
+        <v>616</v>
+      </c>
+      <c r="F26" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A26,合宿走行距離!$B$5:$B$28,$C26)</f>
+        <v>34.2222222222222</v>
+      </c>
+      <c r="G26" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A26,合宿走行距離!$B$5:$B$28,$C26)</f>
+        <v>230</v>
+      </c>
+      <c r="H26" s="18" t="n">
+        <f aca="false">E26+G26</f>
+        <v>846</v>
+      </c>
+      <c r="I26" s="15" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A26,出雲区間記録!$B$5:$B$34,$B26)</f>
+        <v>39.5</v>
+      </c>
+      <c r="J26" s="37" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A26,5000m比較!$C$5:$C$34,$C26)</f>
+        <v>0.0585903775213879</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B27" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="D27" s="14" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A27,5000m比較!$C$5:$C$34,$C27)</f>
+        <v>7</v>
+      </c>
+      <c r="E27" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A27,合宿走行距離!$B$5:$B$28,$C27)</f>
+        <v>501</v>
+      </c>
+      <c r="F27" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A27,合宿走行距離!$B$5:$B$28,$C27)</f>
+        <v>27.8333333333333</v>
+      </c>
+      <c r="G27" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A27,合宿走行距離!$B$5:$B$28,$C27)</f>
+        <v>222</v>
+      </c>
+      <c r="H27" s="18" t="n">
+        <f aca="false">E27+G27</f>
+        <v>723</v>
+      </c>
+      <c r="I27" s="15" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A27,出雲区間記録!$B$5:$B$34,$B27)</f>
+        <v>13.3</v>
+      </c>
+      <c r="J27" s="37" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A27,5000m比較!$C$5:$C$34,$C27)</f>
+        <v>0.0213414634146343</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D28" s="14" t="n">
+        <f aca="false">SUMIFS(5000m比較!$G$5:$G$34,5000m比較!$A$5:$A$34,$A28,5000m比較!$C$5:$C$34,$C28)</f>
+        <v>9</v>
+      </c>
+      <c r="E28" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$C$5:$C$28,合宿走行距離!$A$5:$A$28,$A28,合宿走行距離!$B$5:$B$28,$C28)</f>
+        <v>619</v>
+      </c>
+      <c r="F28" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$F$5:$F$28,合宿走行距離!$A$5:$A$28,$A28,合宿走行距離!$B$5:$B$28,$C28)</f>
+        <v>34.3888888888889</v>
+      </c>
+      <c r="G28" s="18" t="n">
+        <f aca="false">SUMIFS(合宿走行距離!$D$5:$D$28,合宿走行距離!$A$5:$A$28,$A28,合宿走行距離!$B$5:$B$28,$C28)</f>
+        <v>248</v>
+      </c>
+      <c r="H28" s="18" t="n">
+        <f aca="false">E28+G28</f>
+        <v>867</v>
+      </c>
+      <c r="I28" s="15" t="n">
+        <f aca="false">SUMIFS(出雲区間記録!$M$5:$M$34,出雲区間記録!$A$5:$A$34,$A28,出雲区間記録!$B$5:$B$34,$B28)</f>
+        <v>83.3</v>
+      </c>
+      <c r="J28" s="37" t="n">
+        <f aca="false">SUMIFS(5000m比較!$K$5:$K$34,5000m比較!$A$5:$A$34,$A28,5000m比較!$C$5:$C$34,$C28)</f>
+        <v>0.0923172687878573</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="23" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="G31" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="H31" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="I31" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="C32" s="8"/>
+      <c r="D32" s="18" t="n">
+        <f aca="false">AVERAGEIFS($D$5:$D$28,$A$5:$A$28,$A32)</f>
+        <v>4.5</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <f aca="false">AVERAGEIFS($E$5:$E$28,$A$5:$A$28,$A32)</f>
+        <v>575.25</v>
+      </c>
+      <c r="F32" s="18" t="n">
+        <f aca="false">AVERAGEIFS($F$5:$F$28,$A$5:$A$28,$A32)</f>
+        <v>26.1477272727273</v>
+      </c>
+      <c r="G32" s="18" t="n">
+        <f aca="false">AVERAGEIFS($G$5:$G$28,$A$5:$A$28,$A32)</f>
+        <v>232.333333333333</v>
+      </c>
+      <c r="H32" s="18" t="n">
+        <f aca="false">AVERAGEIFS($H$5:$H$28,$A$5:$A$28,$A32)</f>
+        <v>807.583333333333</v>
+      </c>
+      <c r="I32" s="15" t="n">
+        <f aca="false">AVERAGEIFS($I$5:$I$28,$A$5:$A$28,$A32)</f>
+        <v>30.5666666666667</v>
+      </c>
+      <c r="J32" s="17" t="n">
+        <f aca="false">AVERAGEIFS($J$5:$J$28,$A$5:$A$28,$A32)</f>
+        <v>0.0643077124151847</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C33" s="8"/>
+      <c r="D33" s="18" t="n">
+        <f aca="false">AVERAGEIFS($D$5:$D$28,$A$5:$A$28,$A33)</f>
+        <v>3.83333333333333</v>
+      </c>
+      <c r="E33" s="18" t="n">
+        <f aca="false">AVERAGEIFS($E$5:$E$28,$A$5:$A$28,$A33)</f>
+        <v>474.333333333333</v>
+      </c>
+      <c r="F33" s="18" t="n">
+        <f aca="false">AVERAGEIFS($F$5:$F$28,$A$5:$A$28,$A33)</f>
+        <v>24.9649122807018</v>
+      </c>
+      <c r="G33" s="18" t="n">
+        <f aca="false">AVERAGEIFS($G$5:$G$28,$A$5:$A$28,$A33)</f>
+        <v>210.333333333333</v>
+      </c>
+      <c r="H33" s="18" t="n">
+        <f aca="false">AVERAGEIFS($H$5:$H$28,$A$5:$A$28,$A33)</f>
+        <v>684.666666666667</v>
+      </c>
+      <c r="I33" s="15" t="n">
+        <f aca="false">AVERAGEIFS($I$5:$I$28,$A$5:$A$28,$A33)</f>
+        <v>18.6</v>
+      </c>
+      <c r="J33" s="17" t="n">
+        <f aca="false">AVERAGEIFS($J$5:$J$28,$A$5:$A$28,$A33)</f>
+        <v>0.0462450944956439</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="14" t="n">
+        <v>7</v>
+      </c>
+      <c r="C34" s="8"/>
+      <c r="D34" s="18" t="n">
+        <f aca="false">AVERAGEIFS($D$5:$D$28,$A$5:$A$28,$A34)</f>
+        <v>6</v>
+      </c>
+      <c r="E34" s="18" t="n">
+        <f aca="false">AVERAGEIFS($E$5:$E$28,$A$5:$A$28,$A34)</f>
+        <v>578.666666666667</v>
+      </c>
+      <c r="F34" s="18" t="n">
+        <f aca="false">AVERAGEIFS($F$5:$F$28,$A$5:$A$28,$A34)</f>
+        <v>30.4561403508772</v>
+      </c>
+      <c r="G34" s="18" t="n">
+        <f aca="false">AVERAGEIFS($G$5:$G$28,$A$5:$A$28,$A34)</f>
+        <v>230.5</v>
+      </c>
+      <c r="H34" s="18" t="n">
+        <f aca="false">AVERAGEIFS($H$5:$H$28,$A$5:$A$28,$A34)</f>
+        <v>809.166666666667</v>
+      </c>
+      <c r="I34" s="15" t="n">
+        <f aca="false">AVERAGEIFS($I$5:$I$28,$A$5:$A$28,$A34)</f>
+        <v>22.2333333333333</v>
+      </c>
+      <c r="J34" s="17" t="n">
+        <f aca="false">AVERAGEIFS($J$5:$J$28,$A$5:$A$28,$A34)</f>
+        <v>0.052597876567239</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="C35" s="8"/>
+      <c r="D35" s="18" t="n">
+        <f aca="false">AVERAGEIFS($D$5:$D$28,$A$5:$A$28,$A35)</f>
+        <v>8.16666666666667</v>
+      </c>
+      <c r="E35" s="18" t="n">
+        <f aca="false">AVERAGEIFS($E$5:$E$28,$A$5:$A$28,$A35)</f>
+        <v>555.5</v>
+      </c>
+      <c r="F35" s="18" t="n">
+        <f aca="false">AVERAGEIFS($F$5:$F$28,$A$5:$A$28,$A35)</f>
+        <v>30.8611111111111</v>
+      </c>
+      <c r="G35" s="18" t="n">
+        <f aca="false">AVERAGEIFS($G$5:$G$28,$A$5:$A$28,$A35)</f>
+        <v>227.666666666667</v>
+      </c>
+      <c r="H35" s="18" t="n">
+        <f aca="false">AVERAGEIFS($H$5:$H$28,$A$5:$A$28,$A35)</f>
+        <v>783.166666666667</v>
+      </c>
+      <c r="I35" s="15" t="n">
+        <f aca="false">AVERAGEIFS($I$5:$I$28,$A$5:$A$28,$A35)</f>
+        <v>34.1833333333333</v>
+      </c>
+      <c r="J35" s="17" t="n">
+        <f aca="false">AVERAGEIFS($J$5:$J$28,$A$5:$A$28,$A35)</f>
+        <v>0.0518347923041421</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="23" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="11"/>
+      <c r="E38" s="11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="B39" s="7"/>
+      <c r="C39" s="7"/>
+      <c r="D39" s="7"/>
+      <c r="E39" s="21" t="n">
+        <f aca="false">CORREL(E5:E28,D5:D28)</f>
+        <v>0.21035603271837</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="21" t="n">
+        <f aca="false">CORREL(F5:F28,D5:D28)</f>
+        <v>0.3528208001734</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="B41" s="7"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="21" t="n">
+        <f aca="false">CORREL(G5:G28,D5:D28)</f>
+        <v>0.158827292582218</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="B42" s="7"/>
+      <c r="C42" s="7"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="21" t="n">
+        <f aca="false">CORREL(H5:H28,D5:D28)</f>
+        <v>0.221128744912739</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="21" t="n">
+        <f aca="false">CORREL(J5:J28,D5:D28)</f>
+        <v>0.357795231918494</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="38" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="23" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="H47" s="12" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B48" s="8"/>
+      <c r="C48" s="8"/>
+      <c r="D48" s="14" t="n">
+        <f aca="false">COUNTIFS($D$5:$D$28,"&lt;=3")</f>
+        <v>9</v>
+      </c>
+      <c r="E48" s="18" t="n">
+        <f aca="false">AVERAGEIFS(E$5:E$28,$D$5:$D$28,"&lt;=3")</f>
+        <v>529.944444444445</v>
+      </c>
+      <c r="F48" s="18" t="n">
+        <f aca="false">AVERAGEIFS(F$5:F$28,$D$5:$D$28,"&lt;=3")</f>
+        <v>26.6789089727686</v>
+      </c>
+      <c r="G48" s="18" t="n">
+        <f aca="false">AVERAGEIFS(G$5:G$28,$D$5:$D$28,"&lt;=3")</f>
+        <v>216.777777777778</v>
+      </c>
+      <c r="H48" s="18" t="n">
+        <f aca="false">AVERAGEIFS(H$5:H$28,$D$5:$D$28,"&lt;=3")</f>
+        <v>746.722222222222</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="B49" s="8"/>
+      <c r="C49" s="8"/>
+      <c r="D49" s="14" t="n">
+        <f aca="false">COUNTIFS($D$5:$D$28,"&gt;3")</f>
+        <v>15</v>
+      </c>
+      <c r="E49" s="18" t="n">
+        <f aca="false">AVERAGEIFS(E$5:E$28,$D$5:$D$28,"&gt;3")</f>
+        <v>555.533333333333</v>
+      </c>
+      <c r="F49" s="18" t="n">
+        <f aca="false">AVERAGEIFS(F$5:F$28,$D$5:$D$28,"&gt;3")</f>
+        <v>28.9646110225058</v>
+      </c>
+      <c r="G49" s="18" t="n">
+        <f aca="false">AVERAGEIFS(G$5:G$28,$D$5:$D$28,"&gt;3")</f>
+        <v>230.266666666667</v>
+      </c>
+      <c r="H49" s="18" t="n">
+        <f aca="false">AVERAGEIFS(H$5:H$28,$D$5:$D$28,"&gt;3")</f>
+        <v>785.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:J28"/>
+  <mergeCells count="10">
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D5:D28">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="28">
+      <formula>$D5=1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:F28">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <tabColor rgb="FF7FA99B"/>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1:G28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -17645,12 +20496,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -17661,44 +20512,44 @@
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="C5" s="38" t="n">
+        <v>163</v>
+      </c>
+      <c r="C5" s="39" t="n">
         <v>0.614</v>
       </c>
-      <c r="D5" s="38" t="n">
+      <c r="D5" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="38" t="n">
+      <c r="E5" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="39" t="n">
+      <c r="F5" s="40" t="n">
         <f aca="false">IFERROR(AVERAGE(C5:E5),"")</f>
         <v>0.871333333333333</v>
       </c>
@@ -17709,21 +20560,21 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="C6" s="38" t="n">
+        <v>165</v>
+      </c>
+      <c r="C6" s="39" t="n">
         <v>0.9</v>
       </c>
-      <c r="D6" s="38" t="n">
+      <c r="D6" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="38" t="n">
+      <c r="E6" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="39" t="n">
+      <c r="F6" s="40" t="n">
         <f aca="false">IFERROR(AVERAGE(C6:E6),"")</f>
         <v>0.966666666666667</v>
       </c>
@@ -17734,21 +20585,21 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="C7" s="38" t="n">
+        <v>166</v>
+      </c>
+      <c r="C7" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="38" t="n">
+      <c r="D7" s="39" t="n">
         <v>0.825</v>
       </c>
-      <c r="E7" s="38" t="n">
+      <c r="E7" s="39" t="n">
         <v>0.925</v>
       </c>
-      <c r="F7" s="39" t="n">
+      <c r="F7" s="40" t="n">
         <f aca="false">IFERROR(AVERAGE(C7:E7),"")</f>
         <v>0.916666666666667</v>
       </c>
@@ -17759,21 +20610,21 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="C8" s="38" t="n">
+        <v>167</v>
+      </c>
+      <c r="C8" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="38" t="n">
+      <c r="D8" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="38" t="n">
+      <c r="E8" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="39" t="n">
+      <c r="F8" s="40" t="n">
         <f aca="false">IFERROR(AVERAGE(C8:E8),"")</f>
         <v>1</v>
       </c>
@@ -17784,21 +20635,21 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="C9" s="38" t="n">
+        <v>168</v>
+      </c>
+      <c r="C9" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="38" t="n">
+      <c r="D9" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="38" t="n">
+      <c r="E9" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="39" t="n">
+      <c r="F9" s="40" t="n">
         <f aca="false">IFERROR(AVERAGE(C9:E9),"")</f>
         <v>1</v>
       </c>
@@ -17809,21 +20660,21 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="C10" s="38" t="n">
+        <v>169</v>
+      </c>
+      <c r="C10" s="39" t="n">
         <v>0.414</v>
       </c>
-      <c r="D10" s="38" t="n">
+      <c r="D10" s="39" t="n">
         <v>0.925</v>
       </c>
-      <c r="E10" s="38" t="n">
+      <c r="E10" s="39" t="n">
         <v>0.75</v>
       </c>
-      <c r="F10" s="39" t="n">
+      <c r="F10" s="40" t="n">
         <f aca="false">IFERROR(AVERAGE(C10:E10),"")</f>
         <v>0.696333333333333</v>
       </c>
@@ -17834,10 +20685,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C11" s="19" t="n">
         <v>1</v>
@@ -17859,10 +20710,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C12" s="19" t="n">
         <v>1</v>
@@ -17884,10 +20735,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C13" s="19" t="n">
         <v>1</v>
@@ -17909,10 +20760,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C14" s="19" t="n">
         <v>1</v>
@@ -17934,10 +20785,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C15" s="19" t="n">
         <v>0.825</v>
@@ -17959,10 +20810,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C16" s="19" t="n">
         <v>0.925</v>
@@ -17984,21 +20835,21 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="C17" s="38" t="n">
+        <v>175</v>
+      </c>
+      <c r="C17" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="38" t="n">
+      <c r="D17" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="38" t="n">
+      <c r="E17" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="39" t="n">
+      <c r="F17" s="40" t="n">
         <f aca="false">IFERROR(AVERAGE(C17:E17),"")</f>
         <v>1</v>
       </c>
@@ -18009,21 +20860,21 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="C18" s="38" t="n">
+        <v>176</v>
+      </c>
+      <c r="C18" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="38" t="n">
+      <c r="D18" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="38" t="n">
+      <c r="E18" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="39" t="n">
+      <c r="F18" s="40" t="n">
         <f aca="false">IFERROR(AVERAGE(C18:E18),"")</f>
         <v>1</v>
       </c>
@@ -18034,21 +20885,21 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="C19" s="38" t="n">
+        <v>177</v>
+      </c>
+      <c r="C19" s="39" t="n">
         <v>0.66</v>
       </c>
-      <c r="D19" s="38" t="n">
+      <c r="D19" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="38" t="n">
+      <c r="E19" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="39" t="n">
+      <c r="F19" s="40" t="n">
         <f aca="false">IFERROR(AVERAGE(C19:E19),"")</f>
         <v>0.886666666666667</v>
       </c>
@@ -18059,21 +20910,21 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>176</v>
-      </c>
-      <c r="C20" s="38" t="n">
+        <v>178</v>
+      </c>
+      <c r="C20" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="38" t="n">
+      <c r="D20" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="38" t="n">
+      <c r="E20" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="39" t="n">
+      <c r="F20" s="40" t="n">
         <f aca="false">IFERROR(AVERAGE(C20:E20),"")</f>
         <v>1</v>
       </c>
@@ -18084,21 +20935,21 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="C21" s="38" t="n">
+        <v>179</v>
+      </c>
+      <c r="C21" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="38" t="n">
+      <c r="D21" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="38" t="n">
+      <c r="E21" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="39" t="n">
+      <c r="F21" s="40" t="n">
         <f aca="false">IFERROR(AVERAGE(C21:E21),"")</f>
         <v>1</v>
       </c>
@@ -18109,21 +20960,21 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="C22" s="38" t="n">
+        <v>165</v>
+      </c>
+      <c r="C22" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="D22" s="38" t="n">
+      <c r="D22" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="38" t="n">
+      <c r="E22" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="39" t="n">
+      <c r="F22" s="40" t="n">
         <f aca="false">IFERROR(AVERAGE(C22:E22),"")</f>
         <v>1</v>
       </c>
@@ -18134,10 +20985,10 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C23" s="19" t="n">
         <v>0.83</v>
@@ -18159,10 +21010,10 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C24" s="19" t="n">
         <v>1</v>
@@ -18184,10 +21035,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C25" s="19" t="n">
         <v>0.83</v>
@@ -18209,10 +21060,10 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C26" s="19" t="n">
         <v>1</v>
@@ -18234,10 +21085,10 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C27" s="19" t="n">
         <v>1</v>
@@ -18259,10 +21110,10 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C28" s="19" t="n">
         <v>1</v>
@@ -18310,7 +21161,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF7FA99B"/>
@@ -18328,12 +21179,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="9" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -18353,60 +21204,60 @@
     </row>
     <row r="4" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="L4" s="12" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="M4" s="12" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="N4" s="12" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="P4" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C5" s="27" t="n">
         <v>286</v>
@@ -18442,7 +21293,7 @@
       <c r="N5" s="27" t="n">
         <v>478</v>
       </c>
-      <c r="O5" s="40" t="n">
+      <c r="O5" s="41" t="n">
         <f aca="false">IF(OR(J5="",K5="",J5=0),"",K5/J5)</f>
         <v>0.553412462908012</v>
       </c>
@@ -18453,10 +21304,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C6" s="27" t="n">
         <v>370</v>
@@ -18494,7 +21345,7 @@
       <c r="N6" s="27" t="n">
         <v>430</v>
       </c>
-      <c r="O6" s="40" t="n">
+      <c r="O6" s="41" t="n">
         <f aca="false">IF(OR(J6="",K6="",J6=0),"",K6/J6)</f>
         <v>0.540845070422535</v>
       </c>
@@ -18505,10 +21356,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>321</v>
@@ -18546,7 +21397,7 @@
       <c r="N7" s="27" t="n">
         <v>450</v>
       </c>
-      <c r="O7" s="40" t="n">
+      <c r="O7" s="41" t="n">
         <f aca="false">IF(OR(J7="",K7="",J7=0),"",K7/J7)</f>
         <v>0.799373040752351</v>
       </c>
@@ -18557,10 +21408,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B8" s="28" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C8" s="27" t="n">
         <v>126</v>
@@ -18598,7 +21449,7 @@
       <c r="N8" s="27" t="n">
         <v>448</v>
       </c>
-      <c r="O8" s="40" t="n">
+      <c r="O8" s="41" t="n">
         <f aca="false">IF(OR(J8="",K8="",J8=0),"",K8/J8)</f>
         <v>0.550143266475645</v>
       </c>
@@ -18609,10 +21460,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C9" s="27" t="n">
         <v>348</v>
@@ -18650,7 +21501,7 @@
       <c r="N9" s="27" t="n">
         <v>491</v>
       </c>
-      <c r="O9" s="40" t="n">
+      <c r="O9" s="41" t="n">
         <f aca="false">IF(OR(J9="",K9="",J9=0),"",K9/J9)</f>
         <v>0.492063492063492</v>
       </c>
@@ -18661,10 +21512,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C10" s="27" t="n">
         <v>138</v>
@@ -18702,7 +21553,7 @@
       <c r="N10" s="27" t="n">
         <v>345</v>
       </c>
-      <c r="O10" s="40" t="n">
+      <c r="O10" s="41" t="n">
         <f aca="false">IF(OR(J10="",K10="",J10=0),"",K10/J10)</f>
         <v>0.599144079885877</v>
       </c>
@@ -18713,10 +21564,10 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C11" s="14" t="n">
         <v>112</v>
@@ -18761,10 +21612,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C12" s="14" t="n">
         <v>380</v>
@@ -18807,10 +21658,10 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C13" s="14" t="n">
         <v>207</v>
@@ -18855,10 +21706,10 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>353</v>
@@ -18901,10 +21752,10 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
@@ -18947,10 +21798,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C16" s="14" t="n">
         <v>400</v>
@@ -18997,10 +21848,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C17" s="27" t="n">
         <v>284</v>
@@ -19026,7 +21877,7 @@
       <c r="L17" s="27"/>
       <c r="M17" s="27"/>
       <c r="N17" s="27"/>
-      <c r="O17" s="40" t="str">
+      <c r="O17" s="41" t="str">
         <f aca="false">IF(OR(J17="",K17="",J17=0),"",K17/J17)</f>
         <v/>
       </c>
@@ -19037,10 +21888,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C18" s="27" t="n">
         <v>103</v>
@@ -19066,7 +21917,7 @@
       <c r="L18" s="27"/>
       <c r="M18" s="27"/>
       <c r="N18" s="27"/>
-      <c r="O18" s="40" t="str">
+      <c r="O18" s="41" t="str">
         <f aca="false">IF(OR(J18="",K18="",J18=0),"",K18/J18)</f>
         <v/>
       </c>
@@ -19077,10 +21928,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C19" s="27" t="n">
         <v>0</v>
@@ -19106,7 +21957,7 @@
       <c r="L19" s="27"/>
       <c r="M19" s="27"/>
       <c r="N19" s="27"/>
-      <c r="O19" s="40" t="str">
+      <c r="O19" s="41" t="str">
         <f aca="false">IF(OR(J19="",K19="",J19=0),"",K19/J19)</f>
         <v/>
       </c>
@@ -19117,10 +21968,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C20" s="27" t="n">
         <v>175</v>
@@ -19146,7 +21997,7 @@
       <c r="L20" s="27"/>
       <c r="M20" s="27"/>
       <c r="N20" s="27"/>
-      <c r="O20" s="40" t="str">
+      <c r="O20" s="41" t="str">
         <f aca="false">IF(OR(J20="",K20="",J20=0),"",K20/J20)</f>
         <v/>
       </c>
@@ -19157,10 +22008,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C21" s="27" t="n">
         <v>265</v>
@@ -19186,7 +22037,7 @@
       <c r="L21" s="27"/>
       <c r="M21" s="27"/>
       <c r="N21" s="27"/>
-      <c r="O21" s="40" t="str">
+      <c r="O21" s="41" t="str">
         <f aca="false">IF(OR(J21="",K21="",J21=0),"",K21/J21)</f>
         <v/>
       </c>
@@ -19197,10 +22048,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B22" s="28" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C22" s="27" t="n">
         <v>156</v>
@@ -19226,7 +22077,7 @@
       <c r="L22" s="27"/>
       <c r="M22" s="27"/>
       <c r="N22" s="27"/>
-      <c r="O22" s="40" t="str">
+      <c r="O22" s="41" t="str">
         <f aca="false">IF(OR(J22="",K22="",J22=0),"",K22/J22)</f>
         <v/>
       </c>
@@ -19251,7 +22102,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <tabColor rgb="FF7FA99B"/>
@@ -19267,985 +22118,520 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="32" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="41" t="s">
-        <v>210</v>
+      <c r="A2" s="38" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="41" t="s">
-        <v>211</v>
+      <c r="A3" s="38" t="s">
+        <v>232</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="41" t="s">
-        <v>212</v>
+      <c r="A4" s="38" t="s">
+        <v>233</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="42" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="43" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="H12" s="44" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="C13" s="44" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="H13" s="44" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="H14" s="44" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="H15" s="44" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="C16" s="44" t="s">
+        <v>270</v>
+      </c>
+      <c r="D16" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>228</v>
-      </c>
       <c r="E16" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="H16" s="44" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="C18" s="44" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="H18" s="44" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="43" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="11" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="H21" s="11" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="D22" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="F22" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="H22" s="44" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="F23" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="13" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="F24" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="13" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="F25" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="43" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="11" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="F28" s="11" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="H29" s="44" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="D30" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="F30" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H30" s="44" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="F31" s="13" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>233</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <tabColor rgb="FF7FA99B"/>
-    <pageSetUpPr fitToPage="true"/>
-  </sheetPr>
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="15"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="32" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="41" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="41" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="41" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="24" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="42" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="43" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="F12" s="13" t="s">
-        <v>293</v>
-      </c>
-      <c r="G12" s="13" t="s">
-        <v>294</v>
-      </c>
-      <c r="H12" s="44" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>299</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="F14" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="G14" s="13" t="s">
-        <v>302</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="G15" s="44" t="s">
-        <v>306</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="43" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="D19" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="F20" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="G20" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="H21" s="13" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="C22" s="44" t="s">
-        <v>315</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="43" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="11" t="s">
-        <v>217</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>219</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="G25" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="H25" s="11" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="F26" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="H26" s="44" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="13" t="s">
-        <v>276</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="F28" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="G28" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="G29" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>228</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
